--- a/KahootBlank.xlsx
+++ b/KahootBlank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\0W\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26614A8-99E6-4E52-9241-B567ADDABA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06D29C1-AF18-4142-970A-AFCF6D6B2337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20" yWindow="-530" windowWidth="19240" windowHeight="11490" tabRatio="338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
     <t>parent class</t>
   </si>
   <si>
-    <t>Toavoid direct contact AccountManager performs management operations on the BankAccount it is assigned to. This is because it is a_______.</t>
+    <t>AccountManager performs operations on the BankAccount it is assigned to. This is because it is a_______.</t>
   </si>
 </sst>
 </file>
